--- a/tables/slant.xlsx
+++ b/tables/slant.xlsx
@@ -17816,7 +17816,7 @@
         </is>
       </c>
       <c r="C1242" t="n">
-        <v>0.436</v>
+        <v>0.435</v>
       </c>
     </row>
     <row r="1243">

--- a/tables/slant.xlsx
+++ b/tables/slant.xlsx
@@ -17844,7 +17844,7 @@
         </is>
       </c>
       <c r="C1244" t="n">
-        <v>0.435</v>
+        <v>0.434</v>
       </c>
     </row>
     <row r="1245">
